--- a/data/Event_Data_NNB01VR-101.xlsx
+++ b/data/Event_Data_NNB01VR-101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05-10-2569 03:02</t>
+          <t>13-10-2569 05:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22-09-2569 06:58</t>
+          <t>05-10-2569 03:02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,14 +490,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20-09-2569 09:36</t>
+          <t>22-09-2569 06:58</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -512,14 +512,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19-09-2569 11:24</t>
+          <t>20-09-2569 09:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -534,14 +534,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13-09-2569 09:30</t>
+          <t>19-09-2569 11:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09-09-2569 02:19</t>
+          <t>13-09-2569 09:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -578,14 +578,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03-09-2569 21:46</t>
+          <t>09-09-2569 02:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17-08-2569 20:25</t>
+          <t>03-09-2569 21:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L ไม่พบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06-08-2569 03:30</t>
+          <t>17-08-2569 20:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -644,14 +644,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04-08-2569 06:31</t>
+          <t>06-08-2569 03:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -666,14 +666,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ    </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23-07-2569 17:22</t>
+          <t>04-08-2569 06:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T/L, ไม่พบสาเหตุ, จ่ายไฟ, 18.23</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ    </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>23-07-2569 16:14</t>
+          <t>23-07-2569 17:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L, ไม่พบสาเหตุ, จ่ายไฟ, 18.23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14-07-2569 15:56</t>
+          <t>23-07-2569 16:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14-07-2569 13:14</t>
+          <t>14-07-2569 15:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09-07-2569 06:57</t>
+          <t>14-07-2569 13:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04-07-2569 20:26</t>
+          <t>09-07-2569 06:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,19 +793,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/L กิ่งไม้หักพาดหักลูกถ้วยแรงสูง สาย 185 ACSR บ้านนาโดน ห่าง R = 2 กม. จ่ายไฟ 21.57  </t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>23-06-2569 01:38</t>
+          <t>04-07-2569 20:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,19 +815,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t xml:space="preserve">T/L กิ่งไม้หักพาดหักลูกถ้วยแรงสูง สาย 185 ACSR บ้านนาโดน ห่าง R = 2 กม. จ่ายไฟ 21.57  </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20-06-2569 16:04</t>
+          <t>23-06-2569 01:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -842,14 +842,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19-06-2569 04:39</t>
+          <t>20-06-2569 16:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17-06-2569 21:33</t>
+          <t>19-06-2569 04:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -886,14 +886,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16-06-2569 07:04</t>
+          <t>17-06-2569 21:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15-06-2569 02:46</t>
+          <t>16-06-2569 07:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11-06-2569 00:09</t>
+          <t>15-06-2569 02:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>19-05-2569 00:48</t>
+          <t>11-06-2569 00:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18-05-2569 14:04</t>
+          <t>19-05-2569 00:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09-05-2569 22:00</t>
+          <t>18-05-2569 14:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>24-04-2569 11:42</t>
+          <t>09-05-2569 22:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1035,19 +1035,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>T/L กิ่งไม้พาดสาย OHWG หย่อนแตะสายเฟส 185A บ้านชะโอม ห่าง R= 15 กม.</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24-04-2569 11:26</t>
+          <t>24-04-2569 11:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1057,19 +1057,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L กิ่งไม้พาดสาย OHWG หย่อนแตะสายเฟส 185A บ้านชะโอม ห่าง R= 15 กม.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20-03-2569 14:28</t>
+          <t>24-04-2569 11:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1079,19 +1079,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.13</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08-03-2569 20:40</t>
+          <t>20-03-2569 14:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1106,14 +1106,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>T/L กฟจ.นครพนม พบสาเหตุซ๊อตงูที่ต้นอุปกรณ์ตัดตอน รหัส  NNB02VR-103 DS เฟส C</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>18-02-2569 09:14</t>
+          <t>08-03-2569 20:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ปลดฉุกเฉิน แก้ไขต้นไม้หักพาดสายแรงสูง 185 A มีประกายไฟ บ้านนาโทน ห่าง R = 1 กม. จ่ายไฟ 09.16</t>
+          <t>T/L กฟจ.นครพนม พบสาเหตุซ๊อตงูที่ต้นอุปกรณ์ตัดตอน รหัส  NNB02VR-103 DS เฟส C</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06-02-2569 04:54</t>
+          <t>18-02-2569 09:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1145,19 +1145,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>ปลดฉุกเฉิน แก้ไขต้นไม้หักพาดสายแรงสูง 185 A มีประกายไฟ บ้านนาโทน ห่าง R = 1 กม. จ่ายไฟ 09.16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19-01-2569 14:20</t>
+          <t>06-02-2569 04:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06-01-2569 07:12</t>
+          <t>19-01-2569 14:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26-11-2568 03:16</t>
+          <t>06-01-2569 07:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>18-11-2568 22:13</t>
+          <t>26-11-2568 03:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12-11-2568 11:17</t>
+          <t>18-11-2568 22:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1260,14 +1260,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14-10-2568 17:15</t>
+          <t>12-11-2568 11:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1282,14 +1282,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11-10-2568 06:25</t>
+          <t>14-10-2568 17:15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18-09-2568 08:51</t>
+          <t>11-10-2568 06:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>11-09-2568 11:40</t>
+          <t>18-09-2568 08:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09-09-2568 05:51</t>
+          <t>11-09-2568 11:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>24-08-2568 16:22</t>
+          <t>09-09-2568 05:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22-08-2568 02:44</t>
+          <t>24-08-2568 16:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01-08-2568 17:32</t>
+          <t>22-08-2568 02:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1431,19 +1431,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>31-07-2568 23:08</t>
+          <t>01-08-2568 17:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1453,19 +1453,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L ไม่พบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>31-07-2568 21:05</t>
+          <t>31-07-2568 23:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1475,19 +1475,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10-07-2568 21:11</t>
+          <t>31-07-2568 21:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26-05-2568 14:54</t>
+          <t>10-07-2568 21:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1524,14 +1524,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ปลดฉุกเฉิน ย้ายรถยนต์ออกจากจุดเกิดเหตุ เครื่องจักรอยู่ใกล้แนวสายระบบจำหน่าย </t>
+          <t>T/L ไม่พบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19-05-2568 19:09</t>
+          <t>26-05-2568 14:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1541,19 +1541,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">ปลดฉุกเฉิน ย้ายรถยนต์ออกจากจุดเกิดเหตุ เครื่องจักรอยู่ใกล้แนวสายระบบจำหน่าย </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17-03-2568 14:22</t>
+          <t>19-05-2568 19:09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1568,27 +1568,49 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>17-03-2568 14:22</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NNB01VR-101</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>25-01-2568 07:39</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NNB01VR-101</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>T/R</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NNB01VR-101</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
